--- a/用卷/1987.xlsx
+++ b/用卷/1987.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A311F1-7FB5-4C1B-80B9-C1F91B3F65EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4FA06B-BA96-482B-9A8E-8FF9DE82AB5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -219,10 +219,6 @@
     <t>1987年普通高等学校招生全国统一考试用卷情况统计(语数英物化生政史地)</t>
   </si>
   <si>
-    <t>政治为北京卷,其他科目为全国卷</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>政治为天津卷,其他科目为全国卷</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -231,15 +227,19 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>全国卷,北京卷,天津卷,吉林卷,广东卷</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>分科卷数统计</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>英语为MET,物理为广东卷,其他科目为全国卷</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>政治为北师大卷,其他科目为全国卷</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>全国卷,北师大卷,天津卷,吉林卷,广东卷</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -753,7 +753,7 @@
         <v>49</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D4" s="21"/>
     </row>
@@ -777,7 +777,7 @@
         <v>50</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D6" s="15"/>
     </row>
@@ -957,7 +957,7 @@
         <v>11</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D21" s="9"/>
     </row>
@@ -1125,7 +1125,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="22" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B36" s="23"/>
       <c r="C36" s="23"/>
@@ -1187,7 +1187,7 @@
         <v>2</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D41" s="7"/>
     </row>
@@ -1199,7 +1199,7 @@
         <v>2</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D42" s="19"/>
     </row>
@@ -1235,7 +1235,7 @@
         <v>5</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D45" s="7"/>
     </row>
